--- a/tasks/finalpool/pw-canvas-grading-audit-excel-word-email/groundtruth_workspace/Grading_Audit_Report.xlsx
+++ b/tasks/finalpool/pw-canvas-grading-audit-excel-word-email/groundtruth_workspace/Grading_Audit_Report.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -27,26 +27,13 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="004472C4"/>
-        <bgColor rgb="004472C4"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -61,9 +48,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,33 +415,43 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Course</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Code</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Enrollment</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Avg_Score</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Pass_Rate</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>National_Pass_Rate</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Pass_Rate_Gap</t>
         </is>
       </c>
     </row>
@@ -479,6 +475,12 @@
       <c r="E2" t="n">
         <v>83</v>
       </c>
+      <c r="F2" t="n">
+        <v>78.5</v>
+      </c>
+      <c r="G2" t="n">
+        <v>4.5</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -500,6 +502,12 @@
       <c r="E3" t="n">
         <v>72</v>
       </c>
+      <c r="F3" t="n">
+        <v>78.5</v>
+      </c>
+      <c r="G3" t="n">
+        <v>-6.5</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -521,6 +529,12 @@
       <c r="E4" t="n">
         <v>75</v>
       </c>
+      <c r="F4" t="n">
+        <v>71.2</v>
+      </c>
+      <c r="G4" t="n">
+        <v>3.8</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -542,6 +556,12 @@
       <c r="E5" t="n">
         <v>74</v>
       </c>
+      <c r="F5" t="n">
+        <v>71.2</v>
+      </c>
+      <c r="G5" t="n">
+        <v>2.8</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -563,6 +583,12 @@
       <c r="E6" t="n">
         <v>70</v>
       </c>
+      <c r="F6" t="n">
+        <v>71.2</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-1.2</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -583,6 +609,12 @@
       </c>
       <c r="E7" t="n">
         <v>77</v>
+      </c>
+      <c r="F7" t="n">
+        <v>71.2</v>
+      </c>
+      <c r="G7" t="n">
+        <v>5.8</v>
       </c>
     </row>
   </sheetData>
@@ -596,16 +628,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
@@ -649,6 +681,16 @@
       </c>
       <c r="B5" t="n">
         <v>75.2</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Avg_Gap_vs_National</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1.5</v>
       </c>
     </row>
   </sheetData>
@@ -662,21 +704,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Action</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Course</t>
         </is>
@@ -688,12 +730,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Additional support</t>
+          <t>Additional support due to negative gap</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Biochemistry &amp; Bioinformatics (Spring 2013)</t>
+          <t>Applied Analytics &amp; Algorithms (Fall 2014)</t>
         </is>
       </c>
     </row>
@@ -703,12 +745,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Best practices sharing</t>
+          <t>Best practices sharing for high pass rate</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Applied Analytics &amp; Algorithms (Fall 2013)</t>
+          <t>Biochemistry &amp; Bioinformatics (Spring 2014)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Investigate gap</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Biochemistry &amp; Bioinformatics (Spring 2013)</t>
         </is>
       </c>
     </row>
